--- a/05_Yetkili_Kullanıcı_Diary/5 - AU - DR.xlsx
+++ b/05_Yetkili_Kullanıcı_Diary/5 - AU - DR.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\05 - YETKİLİ KULLANICI - DAİRY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC9BD3E-509F-4342-93C8-A44F9485C177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12645BC6-390E-4BF1-8AB2-43DC3B3C7FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="12090" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="5. GEREKSİNİM TAKİP MATRİKSİ" sheetId="10" r:id="rId1"/>
+    <sheet name="5. GEREKSİNİM TAKİP MATRİSİ" sheetId="10" r:id="rId1"/>
     <sheet name="5.1. DIARY SAYFASI İÇERİĞİ" sheetId="1" r:id="rId2"/>
     <sheet name="5.1.1. TARİH SEÇİMİ VE BİÇİMİ" sheetId="2" r:id="rId3"/>
     <sheet name="5.2. PRODUCTS BLOĞU İÇERİĞİ" sheetId="3" r:id="rId4"/>
@@ -478,9 +478,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>Test Type</t>
-  </si>
-  <si>
     <t>Checklist ID</t>
   </si>
   <si>
@@ -494,9 +491,6 @@
   </si>
   <si>
     <t xml:space="preserve">RTM – 005 [AU – DR]	</t>
-  </si>
-  <si>
-    <t>5. Gereksinim Takip Matriksi</t>
   </si>
   <si>
     <t>Yetkili Kullanıcı - Diary</t>
@@ -914,17 +908,31 @@
     <t xml:space="preserve">Tarih Bileşeni Seçimi: gg/aa/yyyy, varsayılan tarih geçerli tarihe eşit.
 </t>
   </si>
+  <si>
+    <t>Document Type</t>
+  </si>
+  <si>
+    <t>5. Gereksinim Takip Matrisi</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1664,384 +1672,387 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2053,11 +2064,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2518,7 +2532,7 @@
   <cols>
     <col min="1" max="1" width="19.1796875" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" customWidth="1"/>
     <col min="4" max="4" width="19.1796875" customWidth="1"/>
     <col min="5" max="5" width="16.453125" customWidth="1"/>
     <col min="6" max="6" width="12.90625" customWidth="1"/>
@@ -2530,8 +2544,8 @@
       <c r="A1" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="69" t="s">
-        <v>119</v>
+      <c r="B1" s="149" t="s">
+        <v>239</v>
       </c>
       <c r="C1" s="69"/>
       <c r="D1" s="69"/>
@@ -2542,7 +2556,7 @@
         <v>104</v>
       </c>
       <c r="B2" s="70" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" s="70"/>
       <c r="F2" s="49" t="s">
@@ -2558,7 +2572,7 @@
         <v>106</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
@@ -2575,7 +2589,7 @@
         <v>108</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C4" s="71"/>
       <c r="F4" s="48" t="s">
@@ -2598,1576 +2612,1576 @@
         <v>112</v>
       </c>
       <c r="C7" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="E7" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="F7" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="G7" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="52" t="s">
-        <v>117</v>
-      </c>
       <c r="H7" s="47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E8" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E9" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H9" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="57" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E10" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H10" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="86" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="57" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C11" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E11" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G11" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="57" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B12" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E12" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H12" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F12" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H12" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C13" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E13" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G13" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="57" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B14" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D14" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E14" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F14" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H14" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="97" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="57" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B15" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E15" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H15" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B16" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E16" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H16" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="97" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="C17" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="E17" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G17" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H17" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="56" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E18" s="53" t="s">
         <v>94</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H18" s="53" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="123" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="56" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B19" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C19" s="59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E19" s="53" t="s">
         <v>94</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G19" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H19" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="57" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E20" s="53" t="s">
         <v>94</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="57" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E21" s="53" t="s">
         <v>94</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G21" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="68.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="57" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D22" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E22" s="53" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H22" s="53" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="59" t="s">
-        <v>162</v>
-      </c>
       <c r="D23" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E23" s="53" t="s">
         <v>94</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G23" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H23" s="53" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="57" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D24" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E24" s="53" t="s">
         <v>94</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H24" s="53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="57" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D25" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E25" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="84.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="57" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D26" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F26" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G26" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H26" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="57" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D27" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E27" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G27" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="57" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D28" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E28" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H28" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="57" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B29" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D29" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E29" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G29" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H29" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="57" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D30" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F30" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G30" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H30" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="57" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B31" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D31" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E31" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F31" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G31" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H31" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="57" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D32" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G32" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H32" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="118" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="57" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B33" s="53" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D33" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E33" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F33" s="53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G33" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H33" s="53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="110" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="57" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D34" s="53" t="s">
         <v>95</v>
       </c>
       <c r="E34" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H34" s="53" t="s">
         <v>143</v>
-      </c>
-      <c r="F34" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G34" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="H34" s="53" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="61" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B35" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C35" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D35" s="62" t="s">
         <v>97</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F35" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G35" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H35" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="61" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B36" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C36" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" s="62" t="s">
         <v>97</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F36" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G36" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H36" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="111" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="61" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B37" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D37" s="62" t="s">
         <v>97</v>
       </c>
       <c r="E37" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F37" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G37" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H37" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="100" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="61" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B38" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C38" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D38" s="62" t="s">
         <v>97</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F38" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G38" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H38" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="106" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="61" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B39" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D39" s="62" t="s">
         <v>97</v>
       </c>
       <c r="E39" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F39" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G39" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H39" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="61" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B40" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C40" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D40" s="62" t="s">
         <v>97</v>
       </c>
       <c r="E40" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F40" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G40" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H40" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="111" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="61" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B41" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C41" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D41" s="62" t="s">
         <v>97</v>
       </c>
       <c r="E41" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="G41" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="H41" s="62" t="s">
         <v>143</v>
-      </c>
-      <c r="F41" s="62" t="s">
-        <v>126</v>
-      </c>
-      <c r="G41" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="H41" s="62" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="137.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="61" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D42" s="64" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E42" s="64" t="s">
         <v>98</v>
       </c>
       <c r="F42" s="67" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G42" s="67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H42" s="64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="153" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="57" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D43" s="64" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E43" s="64" t="s">
         <v>99</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G43" s="67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H43" s="64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="113" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="61" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B44" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C44" s="62" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D44" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E44" s="62" t="s">
         <v>100</v>
       </c>
       <c r="F44" s="67" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G44" s="68" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H44" s="62" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="114.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="61" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B45" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C45" s="62" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D45" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E45" s="62" t="s">
         <v>100</v>
       </c>
       <c r="F45" s="67" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G45" s="68" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H45" s="62" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="60" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C46" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D46" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E46" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F46" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G46" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H46" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I46" s="51"/>
     </row>
     <row r="47" spans="1:9" ht="113.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="60" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B47" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C47" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D47" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E47" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F47" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G47" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H47" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I47" s="51"/>
     </row>
     <row r="48" spans="1:9" ht="110.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B48" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C48" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D48" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G48" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H48" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I48" s="51"/>
     </row>
     <row r="49" spans="1:9" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="60" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B49" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C49" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D49" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E49" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F49" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G49" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H49" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I49" s="51"/>
     </row>
     <row r="50" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="60" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B50" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C50" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D50" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E50" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F50" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G50" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H50" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I50" s="51"/>
     </row>
     <row r="51" spans="1:9" ht="106" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="60" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B51" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C51" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D51" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E51" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F51" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G51" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H51" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I51" s="51"/>
     </row>
     <row r="52" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="60" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B52" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C52" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D52" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E52" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F52" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G52" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H52" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I52" s="51"/>
     </row>
     <row r="53" spans="1:9" ht="127" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="60" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B53" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C53" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D53" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F53" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G53" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H53" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I53" s="51"/>
     </row>
     <row r="54" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="60" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B54" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C54" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D54" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E54" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F54" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H54" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" ht="108.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="60" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B55" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C55" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D55" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F55" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G55" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H55" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="60" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B56" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C56" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D56" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E56" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F56" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G56" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H56" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I56" s="51"/>
     </row>
     <row r="57" spans="1:9" ht="89" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="60" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B57" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C57" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D57" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E57" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F57" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G57" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H57" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I57" s="51"/>
     </row>
     <row r="58" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="60" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B58" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C58" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D58" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E58" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F58" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G58" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H58" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I58" s="51"/>
     </row>
     <row r="59" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="60" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B59" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C59" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D59" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F59" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G59" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H59" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I59" s="51"/>
     </row>
     <row r="60" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="60" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B60" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C60" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D60" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E60" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F60" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G60" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H60" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I60" s="51"/>
     </row>
     <row r="61" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="60" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B61" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C61" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D61" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E61" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F61" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G61" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H61" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I61" s="51"/>
     </row>
     <row r="62" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B62" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C62" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D62" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E62" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F62" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G62" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H62" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I62" s="51"/>
     </row>
     <row r="63" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="60" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B63" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C63" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D63" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E63" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F63" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G63" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H63" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I63" s="51"/>
     </row>
     <row r="64" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="60" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B64" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C64" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D64" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E64" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F64" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G64" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H64" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I64" s="51"/>
     </row>
     <row r="65" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="60" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B65" s="62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C65" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D65" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E65" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F65" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G65" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H65" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I65" s="51"/>
     </row>
     <row r="66" spans="1:9" ht="101" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="60" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B66" s="62" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C66" s="62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D66" s="62" t="s">
         <v>102</v>
       </c>
       <c r="E66" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F66" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G66" s="62" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H66" s="62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I66" s="51"/>
     </row>
@@ -4231,7 +4245,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="73" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" s="73"/>
       <c r="C3" s="24"/>
@@ -4271,7 +4285,7 @@
       <c r="F5" s="74"/>
       <c r="G5" s="74"/>
       <c r="H5" s="75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I5" s="75"/>
       <c r="J5" s="75"/>
@@ -4287,7 +4301,7 @@
       <c r="F6" s="74"/>
       <c r="G6" s="74"/>
       <c r="H6" s="75" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I6" s="75"/>
       <c r="J6" s="75"/>
@@ -4333,30 +4347,30 @@
       <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="141"/>
-      <c r="C10" s="140" t="s">
+      <c r="B10" s="142"/>
+      <c r="C10" s="141" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="142"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="140" t="s">
+      <c r="D10" s="143"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="141" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="142"/>
-      <c r="H10" s="141"/>
-      <c r="I10" s="146" t="s">
-        <v>127</v>
+      <c r="G10" s="143"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="147" t="s">
+        <v>125</v>
       </c>
       <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="140" t="s">
+      <c r="A11" s="141" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="141"/>
+      <c r="B11" s="142"/>
       <c r="C11" s="30" t="s">
         <v>67</v>
       </c>
@@ -4375,11 +4389,11 @@
       <c r="H11" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="147"/>
+      <c r="I11" s="148"/>
       <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="130" t="s">
+      <c r="A12" s="131" t="s">
         <v>71</v>
       </c>
       <c r="B12" s="36" t="s">
@@ -4394,12 +4408,12 @@
       <c r="G12" s="36"/>
       <c r="H12" s="27"/>
       <c r="I12" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J12" s="29"/>
     </row>
     <row r="13" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="131"/>
+      <c r="A13" s="132"/>
       <c r="B13" s="36" t="s">
         <v>85</v>
       </c>
@@ -4412,12 +4426,12 @@
       <c r="G13" s="36"/>
       <c r="H13" s="27"/>
       <c r="I13" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J13" s="29"/>
     </row>
     <row r="14" spans="1:11" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="132"/>
+      <c r="A14" s="133"/>
       <c r="B14" t="s">
         <v>86</v>
       </c>
@@ -4430,12 +4444,12 @@
       <c r="G14" s="36"/>
       <c r="H14" s="27"/>
       <c r="I14" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J14" s="29"/>
     </row>
     <row r="15" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="136" t="s">
+      <c r="A15" s="137" t="s">
         <v>72</v>
       </c>
       <c r="B15" s="36" t="s">
@@ -4450,12 +4464,12 @@
       <c r="G15" s="36"/>
       <c r="H15" s="27"/>
       <c r="I15" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J15" s="29"/>
     </row>
     <row r="16" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="139"/>
+      <c r="A16" s="140"/>
       <c r="B16" s="36" t="s">
         <v>85</v>
       </c>
@@ -4468,12 +4482,12 @@
       <c r="G16" s="35"/>
       <c r="H16" s="27"/>
       <c r="I16" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="138"/>
+      <c r="A17" s="139"/>
       <c r="B17" s="38" t="s">
         <v>86</v>
       </c>
@@ -4486,12 +4500,12 @@
       <c r="G17" s="35"/>
       <c r="H17" s="27"/>
       <c r="I17" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="143" t="s">
+      <c r="A18" s="144" t="s">
         <v>73</v>
       </c>
       <c r="B18" s="36" t="s">
@@ -4506,12 +4520,12 @@
       <c r="G18" s="35"/>
       <c r="H18" s="27"/>
       <c r="I18" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="144"/>
+      <c r="A19" s="145"/>
       <c r="B19" s="36" t="s">
         <v>85</v>
       </c>
@@ -4523,12 +4537,12 @@
       <c r="G19" s="36"/>
       <c r="H19" s="27"/>
       <c r="I19" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="145"/>
+      <c r="A20" s="146"/>
       <c r="B20" t="s">
         <v>86</v>
       </c>
@@ -4541,222 +4555,222 @@
       <c r="G20" s="36"/>
       <c r="H20" s="27"/>
       <c r="I20" s="54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="140" t="s">
+      <c r="A21" s="141" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="141"/>
-      <c r="C21" s="140" t="s">
+      <c r="B21" s="142"/>
+      <c r="C21" s="141" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="142"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="140" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="142"/>
-      <c r="H21" s="141"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="141" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="143"/>
+      <c r="H21" s="142"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="130" t="s">
+      <c r="A22" s="131" t="s">
         <v>76</v>
       </c>
       <c r="B22" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="133" t="s">
+      <c r="C22" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="134"/>
-      <c r="E22" s="135"/>
+      <c r="D22" s="135"/>
+      <c r="E22" s="136"/>
       <c r="F22" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G22" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G22" s="130"/>
       <c r="H22" s="84"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="131"/>
+      <c r="A23" s="132"/>
       <c r="B23" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="133" t="s">
+      <c r="C23" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="134"/>
-      <c r="E23" s="135"/>
+      <c r="D23" s="135"/>
+      <c r="E23" s="136"/>
       <c r="F23" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G23" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G23" s="130"/>
       <c r="H23" s="84"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="131"/>
+      <c r="A24" s="132"/>
       <c r="B24" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="133" t="s">
+      <c r="C24" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="136"/>
       <c r="F24" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G24" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G24" s="130"/>
       <c r="H24" s="84"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="132"/>
+      <c r="A25" s="133"/>
       <c r="B25" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="133" t="s">
+      <c r="C25" s="134" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="134"/>
-      <c r="E25" s="135"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="136"/>
       <c r="F25" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G25" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G25" s="130"/>
       <c r="H25" s="84"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="136" t="s">
+      <c r="A26" s="137" t="s">
         <v>81</v>
       </c>
       <c r="B26" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="133" t="s">
+      <c r="C26" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="134"/>
-      <c r="E26" s="135"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="136"/>
       <c r="F26" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G26" s="130"/>
       <c r="H26" s="84"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="137"/>
+      <c r="A27" s="138"/>
       <c r="B27" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="133" t="s">
+      <c r="C27" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="134"/>
-      <c r="E27" s="135"/>
+      <c r="D27" s="135"/>
+      <c r="E27" s="136"/>
       <c r="F27" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G27" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G27" s="130"/>
       <c r="H27" s="84"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="137"/>
+      <c r="A28" s="138"/>
       <c r="B28" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="133" t="s">
+      <c r="C28" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
+      <c r="D28" s="135"/>
+      <c r="E28" s="136"/>
       <c r="F28" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G28" s="130"/>
       <c r="H28" s="84"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="138"/>
+      <c r="A29" s="139"/>
       <c r="B29" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="133" t="s">
+      <c r="C29" s="134" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="134"/>
-      <c r="E29" s="135"/>
+      <c r="D29" s="135"/>
+      <c r="E29" s="136"/>
       <c r="F29" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G29" s="130"/>
       <c r="H29" s="84"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="130" t="s">
+      <c r="A30" s="131" t="s">
         <v>82</v>
       </c>
       <c r="B30" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="133" t="s">
+      <c r="C30" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="134"/>
-      <c r="E30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="136"/>
       <c r="F30" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G30" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G30" s="130"/>
       <c r="H30" s="84"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="131"/>
+      <c r="A31" s="132"/>
       <c r="B31" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="133" t="s">
+      <c r="C31" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="134"/>
-      <c r="E31" s="135"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="136"/>
       <c r="F31" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G31" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G31" s="130"/>
       <c r="H31" s="84"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="131"/>
+      <c r="A32" s="132"/>
       <c r="B32" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="133" t="s">
+      <c r="C32" s="134" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="134"/>
-      <c r="E32" s="135"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="136"/>
       <c r="F32" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G32" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G32" s="130"/>
       <c r="H32" s="84"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="132"/>
+      <c r="A33" s="133"/>
       <c r="B33" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C33" s="133" t="s">
+      <c r="C33" s="134" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="134"/>
-      <c r="E33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="136"/>
       <c r="F33" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" s="129"/>
+        <v>126</v>
+      </c>
+      <c r="G33" s="130"/>
       <c r="H33" s="84"/>
     </row>
   </sheetData>
@@ -4849,7 +4863,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="73" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" s="73"/>
       <c r="C3" s="4"/>
@@ -4885,7 +4899,7 @@
       </c>
       <c r="B6" s="74"/>
       <c r="C6" s="75" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D6" s="75"/>
       <c r="E6" s="75"/>
@@ -5087,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="88" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E1" s="89"/>
       <c r="F1" s="89"/>
@@ -5106,7 +5120,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F2" s="93"/>
       <c r="G2" s="93"/>
@@ -5129,7 +5143,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="85" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -5187,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C8" s="99"/>
       <c r="D8" s="85" t="s">
@@ -5259,11 +5273,11 @@
         <v>5</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="99"/>
       <c r="D12" s="85" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E12" s="99"/>
       <c r="F12" s="44" t="s">
@@ -5281,7 +5295,7 @@
       </c>
       <c r="C13" s="99"/>
       <c r="D13" s="85" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E13" s="99"/>
       <c r="F13" s="44" t="s">
@@ -5295,11 +5309,11 @@
         <v>7</v>
       </c>
       <c r="B14" s="108" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="109"/>
       <c r="D14" s="108" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E14" s="109"/>
       <c r="F14" s="44" t="s">
@@ -5393,7 +5407,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="73" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" s="73"/>
       <c r="C3" s="4"/>
@@ -5429,7 +5443,7 @@
       </c>
       <c r="B6" s="74"/>
       <c r="C6" s="75" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D6" s="75"/>
       <c r="E6" s="75"/>
@@ -5558,7 +5572,7 @@
     </row>
     <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="83" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B19" s="84"/>
       <c r="C19" s="43" t="s">
@@ -5649,7 +5663,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="73" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" s="73"/>
       <c r="C3" s="4"/>
@@ -5889,7 +5903,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="72" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -5910,7 +5924,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="73" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" s="73"/>
       <c r="C3" s="4"/>
@@ -5946,7 +5960,7 @@
       </c>
       <c r="B6" s="74"/>
       <c r="C6" s="75" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D6" s="75"/>
       <c r="E6" s="75"/>
@@ -5987,7 +6001,7 @@
     </row>
     <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="80" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B11" s="80"/>
       <c r="C11" s="43" t="s">
@@ -5998,7 +6012,7 @@
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="80" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B12" s="80"/>
       <c r="C12" s="43" t="s">
@@ -6009,7 +6023,7 @@
     </row>
     <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="80" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B13" s="80"/>
       <c r="C13" s="43" t="s">
@@ -6020,7 +6034,7 @@
     </row>
     <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="80" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B14" s="80"/>
       <c r="C14" s="43" t="s">
@@ -6031,7 +6045,7 @@
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="80" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B15" s="80"/>
       <c r="C15" s="43" t="s">
@@ -6042,7 +6056,7 @@
     </row>
     <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="80" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B16" s="80"/>
       <c r="C16" s="43" t="s">
@@ -6111,7 +6125,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="88" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E1" s="89"/>
       <c r="F1" s="89"/>
@@ -6130,7 +6144,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F2" s="93"/>
       <c r="G2" s="93"/>
@@ -6167,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="91" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
@@ -6213,11 +6227,11 @@
         <v>1</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C8" s="99"/>
       <c r="D8" s="85" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E8" s="99"/>
       <c r="F8" s="44" t="s">
@@ -6299,40 +6313,40 @@
       <c r="H14" s="21"/>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="117" t="s">
+      <c r="B15" s="117"/>
+      <c r="C15" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="118"/>
+      <c r="D15" s="119"/>
       <c r="E15" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="119">
+      <c r="F15" s="120">
         <v>46229</v>
       </c>
-      <c r="G15" s="120"/>
-      <c r="H15" s="121"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="122"/>
     </row>
     <row r="16" spans="1:8" ht="89" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="113" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B16" s="113"/>
       <c r="C16" s="114" t="s">
-        <v>228</v>
-      </c>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
+        <v>226</v>
+      </c>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
     </row>
     <row r="17" spans="1:8" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="112" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B17" s="112"/>
       <c r="C17" s="111"/>
@@ -6388,7 +6402,8 @@
     <mergeCell ref="C16:H16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6414,7 +6429,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="88" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E1" s="89"/>
       <c r="F1" s="89"/>
@@ -6433,7 +6448,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F2" s="93"/>
       <c r="G2" s="93"/>
@@ -6470,7 +6485,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="91" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
@@ -6516,11 +6531,11 @@
         <v>1</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8" s="99"/>
       <c r="D8" s="85" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E8" s="99"/>
       <c r="F8" s="44" t="s">
@@ -6602,29 +6617,29 @@
       <c r="H14" s="21"/>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="116"/>
+      <c r="B15" s="117"/>
       <c r="C15" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="122" t="s">
+      <c r="D15" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="123"/>
-      <c r="F15" s="126">
+      <c r="E15" s="129"/>
+      <c r="F15" s="125">
         <v>46229</v>
       </c>
-      <c r="G15" s="127"/>
-      <c r="H15" s="128"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="127"/>
     </row>
     <row r="16" spans="1:8" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="125" t="s">
-        <v>222</v>
-      </c>
-      <c r="B16" s="125"/>
-      <c r="C16" s="124" t="e" vm="1">
+      <c r="A16" s="124" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="124"/>
+      <c r="C16" s="123" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="D16" s="111"/>
@@ -6634,8 +6649,8 @@
       <c r="H16" s="111"/>
     </row>
     <row r="17" spans="1:8" ht="240" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="125"/>
-      <c r="B17" s="125"/>
+      <c r="A17" s="124"/>
+      <c r="B17" s="124"/>
       <c r="C17" s="111" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -6647,7 +6662,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="D11:E11"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="B12:C12"/>
@@ -6656,12 +6670,12 @@
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D15:E15"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="A16:B17"/>
     <mergeCell ref="C17:H17"/>
@@ -6677,8 +6691,10 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6704,7 +6720,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="88" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E1" s="89"/>
       <c r="F1" s="89"/>
@@ -6723,7 +6739,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F2" s="93"/>
       <c r="G2" s="93"/>
@@ -6746,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="85" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -6760,7 +6776,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="91" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
@@ -6806,11 +6822,11 @@
         <v>1</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C8" s="99"/>
       <c r="D8" s="85" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E8" s="99"/>
       <c r="F8" s="44" t="s">
@@ -6824,11 +6840,11 @@
         <v>2</v>
       </c>
       <c r="B9" s="85" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C9" s="99"/>
       <c r="D9" s="85" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E9" s="99"/>
       <c r="F9" s="44" t="s">
@@ -6946,5 +6962,6 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>